--- a/設計文件/卡牌資料.xlsx
+++ b/設計文件/卡牌資料.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="卡牌資料" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="填寫說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡牌資料" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="夢境卡" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -29,10 +29,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -42,9 +44,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +71,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
+        <fgColor rgb="FFFFD700"/>
+        <bgColor rgb="FFFFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F4FF"/>
+        <bgColor rgb="FFF0F4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +107,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-        <bgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,7 +141,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -108,9 +149,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -473,30 +549,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" style="15" min="1" max="1"/>
+    <col width="10" customWidth="1" style="15" min="2" max="2"/>
+    <col width="40" customWidth="1" style="15" min="3" max="3"/>
+    <col width="22" customWidth="1" style="15" min="4" max="4"/>
+    <col width="30" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10" customWidth="1" style="15" min="6" max="16"/>
+    <col width="20" customWidth="1" style="15" min="17" max="17"/>
+    <col width="15" customWidth="1" style="15" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="19.95" customHeight="1" s="15">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>卡ID</t>
@@ -512,83 +578,88 @@
           <t>情境</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>條件</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>選項文字</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>聲望</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>金錢</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>裏生命值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>積極</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>理性</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>感性</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>偽善度</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>冷血度</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>壓抑熵</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>靈魂完整度</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>靈魂標記</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>後續事件</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="45" customHeight="1" s="15">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>card_001</t>
@@ -604,137 +675,141 @@
           <t>你十二歲。班上總是被欺負的同學，今天又被圍在角落。輪到你要選邊站了。</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>走過去，站到他旁邊</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>假裝沒看見，繼續玩你的</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="15">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>左</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>試著讓雙方和解，說幾句好話</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="M4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="15">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>跟著其他人一起笑。那樣比較安全</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="15">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>card_002</t>
@@ -750,579 +825,1282 @@
           <t>你二十六歲。一份薪水翻倍的工作機會擺在面前，但必須在四十八小時內決定，沒有時間和任何人商量。</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>接受。人生不等人</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="n">
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="15">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>拒絕。現在的地方還有未竟的事</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="G7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
+      <c r="S7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="15">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>左</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>詢問能否延後決定期限，爭取時間</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="15">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>先口頭答應，回去再找理由反悔</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="n">
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="15">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Hypocrisy&gt;=50</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>答應。至於現在這份工作——讓他們自己想辦法</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="15">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>card_003</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>青年</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>母親打電話說她不舒服，語氣卻輕描淡寫。你知道她從不說自己痛。</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>立刻請假，當天趕回去</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="15">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>等週末再回去看她</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="n">
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="15">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>左</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>打給家裡其他人，請他們先去看看</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="15">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>傳訊問她嚴不嚴重。說你最近很忙</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="n">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="N13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="2" t="n">
+      <c r="O14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>card_004</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>中年</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>你發現，這十年你努力成為的那個人——你其實並不喜歡他。</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>開始做一些改變。小的，但真實的</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="4" t="n">
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="n">
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="15">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>告訴自己這就是成熟，是代價。繼續</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="n">
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="n">
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="n">
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="15">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Entropy&gt;=70</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>你早就知道這個人不是你了。但已經沒差了。繼續</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1" s="15">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>左</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>找一個你信任的人，說出來</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="n">
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="n">
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="15">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>訂了一個旅行計劃。先逃一下再說</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="n">
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="n">
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="15">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>card_005</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>中年</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>有人對你說：「你是我見過最自私的人。」他說的是真的。你知道。</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>沉默，然後離開</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" s="2" t="n">
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="15">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>反駁，列出你所有的付出</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="n">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
         <v>-4</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="O21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" s="15">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>左</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>問他能不能說得更具體一點。你想聽</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="n">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
+      <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="n">
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="15">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>笑著說謝謝，心裡把他列為不重要的人</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n">
         <v>-6</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="N23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="O23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="15">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ruthlessness&gt;=50</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>你微笑，在心裡開始計算他什麼時候會需要你。</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="15">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>card_006</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>童年</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>你最好的朋友開始和另一群人混。他邀你一起，但那群人你不喜歡。</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>硬著頭皮去，朋友比較重要</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" s="15">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>直接說不喜歡那群人</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="16" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N26" s="16" t="n"/>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="16" t="n"/>
+      <c r="Q26" s="16" t="n"/>
+      <c r="R26" s="16" t="n"/>
+      <c r="S26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" s="15">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>假裝很忙，慢慢疏遠</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="16" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1" s="15">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>試著和那群人相處看看，也許沒那麼差</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="16" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="15">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>card_007</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>童年</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>期末考沒考好。父母還不知道。成績單明天就要簽名交回去。</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>主動告訴爸媽，先承認再說</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="18" t="n"/>
+      <c r="R29" s="18" t="n"/>
+      <c r="S29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" s="15">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>自己簽名，能混就混</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" s="18" t="n"/>
+      <c r="P30" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="18" t="n"/>
+      <c r="R30" s="18" t="n"/>
+      <c r="S30" s="18" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" s="15">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>拜託哥哥姊姊幫忙說情</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="18" t="n"/>
+      <c r="R31" s="18" t="n"/>
+      <c r="S31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="15">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>把成績單藏起來，拖到他們忘記</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="18" t="n"/>
+      <c r="R32" s="18" t="n"/>
+      <c r="S32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1" s="15">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>card_008</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>童年</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>同學的筆不見了。你看到另一個同學把它塞進書包——但那個人是班上最受歡迎的。</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>當場說出來，不管後果</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="16" t="n"/>
+      <c r="R33" s="16" t="n"/>
+      <c r="S33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" s="15">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>假裝沒看見。不是你的事</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="16" t="n"/>
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="16" t="n"/>
+      <c r="R34" s="16" t="n"/>
+      <c r="S34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="15">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>私下告訴失主，讓他自己決定</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="16" t="n"/>
+      <c r="L35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="16" t="n"/>
+      <c r="R35" s="16" t="n"/>
+      <c r="S35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="15">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>悄悄告訴老師，不留名字</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="16" t="n"/>
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="16" t="n"/>
+      <c r="Q36" s="16" t="n"/>
+      <c r="R36" s="16" t="n"/>
+      <c r="S36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="15">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>card_009</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>童年</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>你一直很想學畫畫。但父母說那沒有前途，要你去補數學。補習班已經報名了。</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>去補數學。家人的話有道理</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L37" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="18" t="n"/>
+      <c r="R37" s="18" t="n"/>
+      <c r="S37" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>鬧脾氣拒絕，堅持要學畫</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="R38" s="18" t="n"/>
+      <c r="S38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>表面答應，私下找時間偷練</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="18" t="n"/>
+      <c r="R39" s="18" t="n"/>
+      <c r="S39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>認真和父母談，說明為什麼這對你重要</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="18" t="n"/>
+      <c r="R40" s="18" t="n"/>
+      <c r="S40" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1335,243 +2113,1673 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="15" min="1" max="1"/>
+    <col width="14" customWidth="1" style="15" min="2" max="2"/>
+    <col width="42" customWidth="1" style="15" min="3" max="3"/>
+    <col width="6" customWidth="1" style="15" min="4" max="4"/>
+    <col width="32" customWidth="1" style="15" min="5" max="5"/>
+    <col width="10" customWidth="1" style="15" min="6" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.95" customHeight="1" s="15">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>卡ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>觸發維度</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>夢境情境</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>選項文字</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>裏生命值</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>穩定</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>理性</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>感性</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>偽善度</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>冷血度</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>壓抑熵</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>晨間分數</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="15">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>dream_v1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Vitality</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>夢裡你站在水邊。水面映出的不是你的臉，是另一個你——看起來更輕鬆、更完整。</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>伸手觸碰水面</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>轉身離開，不想看</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="15">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>在水邊坐下，靜靜看著那個影像</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="15">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>對著水面說：「我知道了。」</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="15">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>dream_v2</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Vitality</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>夢裡你在奔跑，腿很重，但你繼續跑。你不確定是在追什麼，還是在逃什麼。</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>跑得更快</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="15">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>停下來，喘口氣</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="15">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>問自己：你在逃什麼？</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="15">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>往旁邊轉，換一條路</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="15">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>dream_s1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>夢裡你站在地板裂開的房間。裂縫很細，但一直在擴大。你不確定還能站多久。</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>往裂縫靠近，仔細看它</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="15">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>不動，等著看會怎樣</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="15">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>找最穩的地方站著</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="15">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>大聲呼救</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="15">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>dream_s2</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>夢裡你回到家，但每個房間都比你記得的更小。你越走越擠，幾乎喘不過氣。</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>打開窗子，想讓空間透氣</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>就這樣待在最小的角落</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="15">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>一個一個找你小時候放的東西</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="15">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>走出去，離開這棟房子</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1" s="15">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>dream_d1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>夢裡有一條筆直的路，無限延伸。你站在起點，不知道盡頭有什麼。</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>開始走，不管盡頭</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="15">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>原地等等，也許路會告訴你</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="15">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>問自己：你想去哪裡？</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="15">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>往路旁走，看看有沒有其他方向</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1" s="15">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>dream_d2</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>有人在夢裡遞給你一樣東西，你沒看清楚是什麼。他說：「這是你的。」</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>接過來，先拿再說</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="15">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>謝絕，說你不需要</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="15">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>問：「這是什麼？」</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="15">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>看著它，但遲遲不動</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1" s="15">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>dream_l1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>夢裡有一道題你一直解不開。它懸在空中，黑字白底，靜靜等你。</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>繼續解，絕不放棄</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" s="15">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>闔上眼睛不看它</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" s="15">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>試著改變解題方式</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="15">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>說出聲：「我不知道答案。」</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1" s="15">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>dream_l2</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>夢裡你想說清楚一件事，但說出來的話和你想的不一樣。你試了很多次，都對不上。</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>繼續試，一定有辦法說清楚</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" s="15">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>不說了，讓對方自己去理解</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="15">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>換一種方式表達</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" s="15">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>問對方：「你聽到什麼了？」</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1" s="15">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>dream_e1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>夢裡有人在哭泣，聲音很近，但你找不到他在哪裡。</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>繼續找，直到找到</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="15">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>停下來，也跟著哭</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="15">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>出聲說：「我在這裡。」</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="15">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>告訴自己和自己沒關係，離開</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1" s="15">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>dream_e2</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>夢裡你想對某個人說「對不起」，但對象的臉模糊了，你不確定是誰。</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>說出來，不管對象是誰</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" s="15">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>算了，也許說了也沒用</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" s="15">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>試著想清楚，這個歉意是給誰的</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" s="15">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>只是站著，讓那份歉意留著</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="15" min="1" max="1"/>
+    <col width="60" customWidth="1" style="15" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="25.05" customHeight="1" s="15">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>卡牌填寫說明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="15">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>卡ID</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>唯一識別碼，格式建議：card_XXX（三位數字），每張新卡只填第一行</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="15">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>年齡池</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>童年 / 青年 / 中年 / 老年（每張新卡只填第一行）</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5" ht="30" customHeight="1" s="15">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>情境</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>顯示在卡牌中央的情境描述（每張新卡只填第一行）</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6" ht="30" customHeight="1" s="15">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>上 / 下 / 左 / 右，每張卡需填滿四行</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="15">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>選項文字</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>玩家選擇時看到的文字描述</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="15">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>聲望</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>社會表層數值，可正可負，留空代表此選項不影響此數值</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="15">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>金錢</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>社會表層數值，可正可負，留空代表此選項不影響此數值</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="15">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>裏生命值</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>核心數值，可正可負，留空代表不影響</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="15">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>核心數值（Stability）</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="15">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>積極</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>核心數值（Drive）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="15">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>理性</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>核心數值（Logic）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="15">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>感性</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>核心數值（Emotion）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>偽善度</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>靈魂毒素（Hypocrisy），通常為正值（毒素累積）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="16" ht="30" customHeight="1" s="15">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>冷血度</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>靈魂毒素（Ruthlessness）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="15">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>壓抑熵</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>靈魂毒素（Entropy），負值代表毒素淨化</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="18" ht="30" customHeight="1" s="15">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>靈魂完整度</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>直接影響靈魂完整度的特殊效果，通常為負值</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="15">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>靈魂標記</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>多個標記用逗號分隔，例如：放下,原諒。留空代表無標記</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="15">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>後續事件</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>故事鏈ID，留空代表正常繼續。例如：story_001</t>
         </is>

--- a/設計文件/卡牌資料.xlsx
+++ b/設計文件/卡牌資料.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡牌資料" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="夢境卡" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="壓力牌" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="故事鏈牌" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -72,8 +73,16 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +136,11 @@
         <fgColor rgb="FF2C3E6B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -155,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +231,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -587,17 +604,17 @@
   <dimension ref="A1:S220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="24" min="1" max="1"/>
-    <col width="10" customWidth="1" style="24" min="2" max="2"/>
-    <col width="40" customWidth="1" style="24" min="3" max="3"/>
-    <col width="22" customWidth="1" style="24" min="4" max="4"/>
-    <col width="30" customWidth="1" style="24" min="5" max="5"/>
-    <col width="10" customWidth="1" style="24" min="6" max="16"/>
-    <col width="20" customWidth="1" style="24" min="17" max="17"/>
-    <col width="15" customWidth="1" style="24" min="18" max="18"/>
+    <col width="12" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="40" customWidth="1" style="25" min="3" max="3"/>
+    <col width="22" customWidth="1" style="25" min="4" max="4"/>
+    <col width="30" customWidth="1" style="25" min="5" max="5"/>
+    <col width="10" customWidth="1" style="25" min="6" max="16"/>
+    <col width="20" customWidth="1" style="25" min="17" max="17"/>
+    <col width="15" customWidth="1" style="25" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.95" customHeight="1" s="24">
+    <row r="1" ht="19.95" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>卡ID</t>
@@ -694,7 +711,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1" s="24">
+    <row r="2" ht="45" customHeight="1" s="25">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>card_001</t>
@@ -741,7 +758,7 @@
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1" s="24">
+    <row r="3" ht="30" customHeight="1" s="25">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="3" t="n"/>
@@ -774,7 +791,7 @@
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="24">
+    <row r="4" ht="30" customHeight="1" s="25">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="3" t="n"/>
@@ -809,7 +826,7 @@
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="24">
+    <row r="5" ht="30" customHeight="1" s="25">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
@@ -844,7 +861,7 @@
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
     </row>
-    <row r="6" ht="45" customHeight="1" s="24">
+    <row r="6" ht="45" customHeight="1" s="25">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>card_002</t>
@@ -891,7 +908,7 @@
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="24">
+    <row r="7" ht="30" customHeight="1" s="25">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="5" t="n"/>
@@ -926,7 +943,7 @@
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="24">
+    <row r="8" ht="30" customHeight="1" s="25">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="5" t="n"/>
@@ -959,7 +976,7 @@
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="24">
+    <row r="9" ht="30" customHeight="1" s="25">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="5" t="n"/>
@@ -994,7 +1011,7 @@
       <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1" s="24">
+    <row r="10" ht="45" customHeight="1" s="25">
       <c r="D10" t="inlineStr">
         <is>
           <t>Hypocrisy&gt;=50</t>
@@ -1023,7 +1040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="24">
+    <row r="11" ht="30" customHeight="1" s="25">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>card_003</t>
@@ -1070,7 +1087,7 @@
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="24">
+    <row r="12" ht="30" customHeight="1" s="25">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="3" t="n"/>
@@ -1105,7 +1122,7 @@
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="24">
+    <row r="13" ht="30" customHeight="1" s="25">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="3" t="n"/>
@@ -1138,7 +1155,7 @@
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
     </row>
-    <row r="14" ht="45" customHeight="1" s="24">
+    <row r="14" ht="45" customHeight="1" s="25">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="3" t="n"/>
@@ -1173,7 +1190,7 @@
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="24">
+    <row r="15" ht="30" customHeight="1" s="25">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>card_004</t>
@@ -1220,7 +1237,7 @@
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="24">
+    <row r="16" ht="30" customHeight="1" s="25">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="5" t="n"/>
@@ -1255,7 +1272,7 @@
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1" s="24">
+    <row r="17" ht="30" customHeight="1" s="25">
       <c r="D17" t="inlineStr">
         <is>
           <t>Entropy&gt;=70</t>
@@ -1281,7 +1298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1" s="24">
+    <row r="18" ht="45" customHeight="1" s="25">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="5" t="n"/>
@@ -1316,7 +1333,7 @@
       <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="24">
+    <row r="19" ht="30" customHeight="1" s="25">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="5" t="n"/>
@@ -1351,7 +1368,7 @@
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="24">
+    <row r="20" ht="30" customHeight="1" s="25">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>card_005</t>
@@ -1398,7 +1415,7 @@
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="24">
+    <row r="21" ht="30" customHeight="1" s="25">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="3" t="n"/>
@@ -1433,7 +1450,7 @@
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1" s="24">
+    <row r="22" ht="45" customHeight="1" s="25">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="3" t="n"/>
@@ -1470,7 +1487,7 @@
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1" s="24">
+    <row r="23" ht="30" customHeight="1" s="25">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="3" t="n"/>
@@ -1505,7 +1522,7 @@
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1" s="24">
+    <row r="24" ht="30" customHeight="1" s="25">
       <c r="D24" t="inlineStr">
         <is>
           <t>Ruthlessness&gt;=50</t>
@@ -1531,7 +1548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="24">
+    <row r="25" ht="30" customHeight="1" s="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>card_006</t>
@@ -1578,7 +1595,7 @@
       <c r="R25" s="14" t="n"/>
       <c r="S25" s="14" t="n"/>
     </row>
-    <row r="26" ht="45" customHeight="1" s="24">
+    <row r="26" ht="45" customHeight="1" s="25">
       <c r="A26" s="14" t="n"/>
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="15" t="n"/>
@@ -1613,7 +1630,7 @@
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="14" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1" s="24">
+    <row r="27" ht="30" customHeight="1" s="25">
       <c r="A27" s="14" t="n"/>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="15" t="n"/>
@@ -1648,7 +1665,7 @@
       <c r="R27" s="14" t="n"/>
       <c r="S27" s="14" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1" s="24">
+    <row r="28" ht="30" customHeight="1" s="25">
       <c r="A28" s="14" t="n"/>
       <c r="B28" s="14" t="n"/>
       <c r="C28" s="15" t="n"/>
@@ -1683,7 +1700,7 @@
       <c r="R28" s="14" t="n"/>
       <c r="S28" s="14" t="n"/>
     </row>
-    <row r="29" ht="30" customHeight="1" s="24">
+    <row r="29" ht="30" customHeight="1" s="25">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>card_007</t>
@@ -1728,7 +1745,7 @@
       <c r="R29" s="16" t="n"/>
       <c r="S29" s="16" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1" s="24">
+    <row r="30" ht="45" customHeight="1" s="25">
       <c r="A30" s="16" t="n"/>
       <c r="B30" s="16" t="n"/>
       <c r="C30" s="17" t="n"/>
@@ -1763,7 +1780,7 @@
       <c r="R30" s="16" t="n"/>
       <c r="S30" s="16" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1" s="24">
+    <row r="31" ht="30" customHeight="1" s="25">
       <c r="A31" s="16" t="n"/>
       <c r="B31" s="16" t="n"/>
       <c r="C31" s="17" t="n"/>
@@ -1798,7 +1815,7 @@
       <c r="R31" s="16" t="n"/>
       <c r="S31" s="16" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="24">
+    <row r="32" ht="30" customHeight="1" s="25">
       <c r="A32" s="16" t="n"/>
       <c r="B32" s="16" t="n"/>
       <c r="C32" s="17" t="n"/>
@@ -1835,7 +1852,7 @@
       <c r="R32" s="16" t="n"/>
       <c r="S32" s="16" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1" s="24">
+    <row r="33" ht="30" customHeight="1" s="25">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>card_008</t>
@@ -1882,7 +1899,7 @@
       <c r="R33" s="14" t="n"/>
       <c r="S33" s="14" t="n"/>
     </row>
-    <row r="34" ht="45" customHeight="1" s="24">
+    <row r="34" ht="45" customHeight="1" s="25">
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="14" t="n"/>
       <c r="C34" s="15" t="n"/>
@@ -1917,7 +1934,7 @@
       <c r="R34" s="14" t="n"/>
       <c r="S34" s="14" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1" s="24">
+    <row r="35" ht="30" customHeight="1" s="25">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="14" t="n"/>
       <c r="C35" s="15" t="n"/>
@@ -1950,7 +1967,7 @@
       <c r="R35" s="14" t="n"/>
       <c r="S35" s="14" t="n"/>
     </row>
-    <row r="36" ht="30" customHeight="1" s="24">
+    <row r="36" ht="30" customHeight="1" s="25">
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="14" t="n"/>
       <c r="C36" s="15" t="n"/>
@@ -1983,7 +2000,7 @@
       <c r="R36" s="14" t="n"/>
       <c r="S36" s="14" t="n"/>
     </row>
-    <row r="37" ht="30" customHeight="1" s="24">
+    <row r="37" ht="30" customHeight="1" s="25">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>card_009</t>
@@ -2032,7 +2049,7 @@
       <c r="R37" s="16" t="n"/>
       <c r="S37" s="16" t="n"/>
     </row>
-    <row r="38" ht="41.4" customHeight="1" s="24">
+    <row r="38" ht="41.4" customHeight="1" s="25">
       <c r="A38" s="16" t="n"/>
       <c r="B38" s="16" t="n"/>
       <c r="C38" s="17" t="n"/>
@@ -2067,7 +2084,7 @@
       <c r="R38" s="16" t="n"/>
       <c r="S38" s="16" t="n"/>
     </row>
-    <row r="39" ht="41.4" customHeight="1" s="24">
+    <row r="39" ht="41.4" customHeight="1" s="25">
       <c r="A39" s="16" t="n"/>
       <c r="B39" s="16" t="n"/>
       <c r="C39" s="17" t="n"/>
@@ -2102,7 +2119,7 @@
       <c r="R39" s="16" t="n"/>
       <c r="S39" s="16" t="n"/>
     </row>
-    <row r="40" ht="69" customHeight="1" s="24">
+    <row r="40" ht="69" customHeight="1" s="25">
       <c r="A40" s="16" t="n"/>
       <c r="B40" s="16" t="n"/>
       <c r="C40" s="17" t="n"/>
@@ -2137,6 +2154,7 @@
       <c r="R40" s="16" t="n"/>
       <c r="S40" s="16" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -2233,6 +2251,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -2329,6 +2348,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -2425,6 +2445,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -2512,6 +2533,7 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -2602,6 +2624,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -2692,6 +2715,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -2782,6 +2806,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -2872,6 +2897,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -2962,6 +2988,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -3058,6 +3085,7 @@
         <v>-3</v>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -3151,6 +3179,7 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -3244,6 +3273,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -3340,6 +3370,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
@@ -3430,6 +3461,7 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -3520,6 +3552,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="116"/>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
@@ -3613,6 +3646,7 @@
         <v>-3</v>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -3703,6 +3737,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
@@ -3796,6 +3831,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -3889,6 +3925,7 @@
         <v>-3</v>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -3982,6 +4019,7 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -4078,6 +4116,7 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="146"/>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
@@ -4109,6 +4148,11 @@
       </c>
       <c r="P147" t="n">
         <v>-3</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>sc_001</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -5496,15 +5540,15 @@
   <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="24" min="1" max="1"/>
-    <col width="14" customWidth="1" style="24" min="2" max="2"/>
-    <col width="42" customWidth="1" style="24" min="3" max="3"/>
-    <col width="6" customWidth="1" style="24" min="4" max="4"/>
-    <col width="32" customWidth="1" style="24" min="5" max="5"/>
-    <col width="10" customWidth="1" style="24" min="6" max="14"/>
+    <col width="12" customWidth="1" style="25" min="1" max="1"/>
+    <col width="14" customWidth="1" style="25" min="2" max="2"/>
+    <col width="42" customWidth="1" style="25" min="3" max="3"/>
+    <col width="6" customWidth="1" style="25" min="4" max="4"/>
+    <col width="32" customWidth="1" style="25" min="5" max="5"/>
+    <col width="10" customWidth="1" style="25" min="6" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.95" customHeight="1" s="24">
+    <row r="1" ht="19.95" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>卡ID</t>
@@ -5576,7 +5620,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1" s="24">
+    <row r="2" ht="45" customHeight="1" s="25">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>dream_v1</t>
@@ -5618,7 +5662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="24">
+    <row r="3" ht="30" customHeight="1" s="25">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="3" t="n"/>
@@ -5648,7 +5692,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="24">
+    <row r="4" ht="30" customHeight="1" s="25">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="3" t="n"/>
@@ -5678,7 +5722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="24">
+    <row r="5" ht="30" customHeight="1" s="25">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
@@ -5710,7 +5754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="24">
+    <row r="6" ht="45" customHeight="1" s="25">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>dream_v2</t>
@@ -5752,7 +5796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="24">
+    <row r="7" ht="30" customHeight="1" s="25">
       <c r="A7" s="11" t="n"/>
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="12" t="n"/>
@@ -5782,7 +5826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="24">
+    <row r="8" ht="30" customHeight="1" s="25">
       <c r="A8" s="11" t="n"/>
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="12" t="n"/>
@@ -5812,7 +5856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="24">
+    <row r="9" ht="30" customHeight="1" s="25">
       <c r="A9" s="11" t="n"/>
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="12" t="n"/>
@@ -5842,7 +5886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" s="24">
+    <row r="10" ht="45" customHeight="1" s="25">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>dream_s1</t>
@@ -5884,7 +5928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="24">
+    <row r="11" ht="30" customHeight="1" s="25">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="3" t="n"/>
@@ -5914,7 +5958,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="24">
+    <row r="12" ht="30" customHeight="1" s="25">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="3" t="n"/>
@@ -5944,7 +5988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="24">
+    <row r="13" ht="30" customHeight="1" s="25">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="3" t="n"/>
@@ -5974,7 +6018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1" s="24">
+    <row r="14" ht="45" customHeight="1" s="25">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>dream_s2</t>
@@ -6016,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="24">
+    <row r="15" ht="30" customHeight="1" s="25">
       <c r="A15" s="11" t="n"/>
       <c r="B15" s="11" t="n"/>
       <c r="C15" s="12" t="n"/>
@@ -6046,7 +6090,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="24">
+    <row r="16" ht="30" customHeight="1" s="25">
       <c r="A16" s="11" t="n"/>
       <c r="B16" s="11" t="n"/>
       <c r="C16" s="12" t="n"/>
@@ -6076,7 +6120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="24">
+    <row r="17" ht="30" customHeight="1" s="25">
       <c r="A17" s="11" t="n"/>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="12" t="n"/>
@@ -6108,7 +6152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1" s="24">
+    <row r="18" ht="45" customHeight="1" s="25">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>dream_d1</t>
@@ -6150,7 +6194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="24">
+    <row r="19" ht="30" customHeight="1" s="25">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="3" t="n"/>
@@ -6180,7 +6224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="24">
+    <row r="20" ht="30" customHeight="1" s="25">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="3" t="n"/>
@@ -6210,7 +6254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="24">
+    <row r="21" ht="30" customHeight="1" s="25">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="3" t="n"/>
@@ -6240,7 +6284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1" s="24">
+    <row r="22" ht="45" customHeight="1" s="25">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>dream_d2</t>
@@ -6282,7 +6326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="24">
+    <row r="23" ht="30" customHeight="1" s="25">
       <c r="A23" s="11" t="n"/>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="12" t="n"/>
@@ -6312,7 +6356,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="24">
+    <row r="24" ht="30" customHeight="1" s="25">
       <c r="A24" s="11" t="n"/>
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="12" t="n"/>
@@ -6342,7 +6386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="24">
+    <row r="25" ht="30" customHeight="1" s="25">
       <c r="A25" s="11" t="n"/>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="12" t="n"/>
@@ -6372,7 +6416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1" s="24">
+    <row r="26" ht="45" customHeight="1" s="25">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>dream_l1</t>
@@ -6416,7 +6460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="24">
+    <row r="27" ht="30" customHeight="1" s="25">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="3" t="n"/>
@@ -6446,7 +6490,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="24">
+    <row r="28" ht="30" customHeight="1" s="25">
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="3" t="n"/>
@@ -6478,7 +6522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="24">
+    <row r="29" ht="30" customHeight="1" s="25">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="3" t="n"/>
@@ -6508,7 +6552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1" s="24">
+    <row r="30" ht="45" customHeight="1" s="25">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>dream_l2</t>
@@ -6550,7 +6594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="24">
+    <row r="31" ht="30" customHeight="1" s="25">
       <c r="A31" s="11" t="n"/>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="12" t="n"/>
@@ -6580,7 +6624,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="24">
+    <row r="32" ht="30" customHeight="1" s="25">
       <c r="A32" s="11" t="n"/>
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="12" t="n"/>
@@ -6612,7 +6656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="24">
+    <row r="33" ht="30" customHeight="1" s="25">
       <c r="A33" s="11" t="n"/>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="12" t="n"/>
@@ -6642,7 +6686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1" s="24">
+    <row r="34" ht="45" customHeight="1" s="25">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>dream_e1</t>
@@ -6686,7 +6730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="24">
+    <row r="35" ht="30" customHeight="1" s="25">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="3" t="n"/>
@@ -6716,7 +6760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="24">
+    <row r="36" ht="30" customHeight="1" s="25">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="3" t="n"/>
@@ -6746,7 +6790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" s="24">
+    <row r="37" ht="30" customHeight="1" s="25">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="3" t="n"/>
@@ -6776,7 +6820,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1" s="24">
+    <row r="38" ht="45" customHeight="1" s="25">
       <c r="A38" s="11" t="inlineStr">
         <is>
           <t>dream_e2</t>
@@ -6820,7 +6864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" s="24">
+    <row r="39" ht="30" customHeight="1" s="25">
       <c r="A39" s="11" t="n"/>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="n"/>
@@ -6850,7 +6894,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="24">
+    <row r="40" ht="30" customHeight="1" s="25">
       <c r="A40" s="11" t="n"/>
       <c r="B40" s="11" t="n"/>
       <c r="C40" s="12" t="n"/>
@@ -6882,7 +6926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" s="24">
+    <row r="41" ht="30" customHeight="1" s="25">
       <c r="A41" s="11" t="n"/>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="12" t="n"/>
@@ -6926,12 +6970,12 @@
   <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="24" min="1" max="1"/>
-    <col width="10" customWidth="1" style="24" min="2" max="2"/>
-    <col width="8" customWidth="1" style="24" min="3" max="3"/>
-    <col width="50" customWidth="1" style="24" min="4" max="4"/>
-    <col width="6" customWidth="1" style="24" min="5" max="5"/>
-    <col width="40" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="8" customWidth="1" style="25" min="3" max="3"/>
+    <col width="50" customWidth="1" style="25" min="4" max="4"/>
+    <col width="6" customWidth="1" style="25" min="5" max="5"/>
+    <col width="40" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8446,21 +8490,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="40" customWidth="1" style="25" min="3" max="3"/>
+    <col width="6" customWidth="1" style="25" min="4" max="4"/>
+    <col width="24" customWidth="1" style="25" min="5" max="5"/>
+    <col width="10" customWidth="1" style="25" min="6" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>鏈ID</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>卡ID</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>情境</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>選項文字</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>下一張</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>結束今日</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>聲望</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>金錢</t>
+        </is>
+      </c>
+      <c r="J1" s="23" t="inlineStr">
+        <is>
+          <t>裏生命值</t>
+        </is>
+      </c>
+      <c r="K1" s="23" t="inlineStr">
+        <is>
+          <t>穩定</t>
+        </is>
+      </c>
+      <c r="L1" s="23" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t>理性</t>
+        </is>
+      </c>
+      <c r="N1" s="23" t="inlineStr">
+        <is>
+          <t>感性</t>
+        </is>
+      </c>
+      <c r="O1" s="23" t="inlineStr">
+        <is>
+          <t>偽善度</t>
+        </is>
+      </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>冷血度</t>
+        </is>
+      </c>
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>壓抑熵</t>
+        </is>
+      </c>
+      <c r="R1" s="23" t="inlineStr">
+        <is>
+          <t>靈魂完整度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>chain_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sc_001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>你把事情說清楚了。媽媽沒有立刻回應，沉默了一會兒。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>繼續等她說話</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sc_002</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>說你知道這樣不對</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sc_002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>忍不住又道了一次歉</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sc_002</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>問她是不是很失望</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sc_003</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sc_002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>媽媽說：「我知道你想要那個東西。但你應該來告訴我。」</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>說你以後會直接問</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>說對不起</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>點頭，什麼都沒說</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>問她能不能原諒你</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sc_003</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>她說：「我知道你有時候怕開口。但我希望你不要用這種方式。」</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>說你懂了</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>問她為什麼覺得你怕開口</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>說你不知道為什麼沒說</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>沉默</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" style="24" min="1" max="1"/>
-    <col width="60" customWidth="1" style="24" min="2" max="2"/>
+    <col width="15" customWidth="1" style="25" min="1" max="1"/>
+    <col width="60" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.05" customHeight="1" s="24">
-      <c r="A1" s="23" t="inlineStr">
+    <row r="1" ht="25.05" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>卡牌填寫說明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="24">
+    <row r="2" ht="30" customHeight="1" s="25">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>欄位</t>
@@ -8472,7 +8934,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="24">
+    <row r="3" ht="30" customHeight="1" s="25">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>卡ID</t>
@@ -8484,7 +8946,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="24">
+    <row r="4" ht="30" customHeight="1" s="25">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>年齡池</t>
@@ -8496,7 +8958,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="24">
+    <row r="5" ht="30" customHeight="1" s="25">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>情境</t>
@@ -8508,7 +8970,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="24">
+    <row r="6" ht="30" customHeight="1" s="25">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>方向</t>
@@ -8520,7 +8982,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="24">
+    <row r="7" ht="30" customHeight="1" s="25">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>選項文字</t>
@@ -8532,7 +8994,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="24">
+    <row r="8" ht="30" customHeight="1" s="25">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>聲望</t>
@@ -8544,7 +9006,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="24">
+    <row r="9" ht="30" customHeight="1" s="25">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>金錢</t>
@@ -8556,7 +9018,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="24">
+    <row r="10" ht="30" customHeight="1" s="25">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>裏生命值</t>
@@ -8568,7 +9030,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="24">
+    <row r="11" ht="30" customHeight="1" s="25">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>穩定</t>
@@ -8580,7 +9042,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="24">
+    <row r="12" ht="30" customHeight="1" s="25">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>積極</t>
@@ -8592,7 +9054,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="24">
+    <row r="13" ht="30" customHeight="1" s="25">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>理性</t>
@@ -8604,7 +9066,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="24">
+    <row r="14" ht="30" customHeight="1" s="25">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>感性</t>
@@ -8616,7 +9078,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="24">
+    <row r="15" ht="30" customHeight="1" s="25">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>偽善度</t>
@@ -8628,7 +9090,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="24">
+    <row r="16" ht="30" customHeight="1" s="25">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>冷血度</t>
@@ -8640,7 +9102,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="24">
+    <row r="17" ht="30" customHeight="1" s="25">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>壓抑熵</t>
@@ -8652,7 +9114,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="24">
+    <row r="18" ht="30" customHeight="1" s="25">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>靈魂完整度</t>
@@ -8664,7 +9126,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="24">
+    <row r="19" ht="30" customHeight="1" s="25">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>靈魂標記</t>
@@ -8676,7 +9138,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="24">
+    <row r="20" ht="30" customHeight="1" s="25">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>後續事件</t>
